--- a/templates_formats/carnet.xlsx
+++ b/templates_formats/carnet.xlsx
@@ -54,14 +54,14 @@
     <t>MINISTERIO "NOMBRE MINISTERIO"</t>
   </si>
   <si>
-    <t>"NOMBRE MUNICIPIO","NOMBRE ESTADO"</t>
+    <t>NOMBRE MUNICIPIO,"NOMBRE ESTADO"</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -77,13 +77,6 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <sz val="8"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -93,7 +86,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="8">
     <border>
       <left/>
       <right/>
@@ -110,11 +103,71 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
@@ -132,21 +185,9 @@
       <alignment horizontal="left" indent="4"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" indent="30"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" indent="26"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" indent="30"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -156,20 +197,41 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" indent="23"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" indent="18"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" indent="16"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" indent="12"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" indent="19"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -472,350 +534,448 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B1:M66"/>
+  <dimension ref="B1:P66"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="2.25" customWidth="1"/>
-    <col min="2" max="2" width="1.625" customWidth="1"/>
-    <col min="3" max="3" width="9.5" customWidth="1"/>
-    <col min="4" max="4" width="30.625" customWidth="1"/>
-    <col min="5" max="5" width="30.125" customWidth="1"/>
-    <col min="6" max="6" width="11.25" customWidth="1"/>
-    <col min="7" max="7" width="10.25" customWidth="1"/>
-    <col min="8" max="8" width="8.375" customWidth="1"/>
-    <col min="9" max="9" width="25.875" customWidth="1"/>
-    <col min="10" max="10" width="5.75" customWidth="1"/>
-    <col min="11" max="11" width="2.5" customWidth="1"/>
-    <col min="12" max="12" width="8.125" customWidth="1"/>
+    <col min="2" max="2" width="33.625" customWidth="1"/>
+    <col min="3" max="3" width="1.375" customWidth="1"/>
+    <col min="4" max="4" width="12" customWidth="1"/>
+    <col min="5" max="5" width="1.125" customWidth="1"/>
+    <col min="6" max="6" width="38.25" customWidth="1"/>
+    <col min="7" max="7" width="3.625" customWidth="1"/>
+    <col min="8" max="8" width="3.125" customWidth="1"/>
+    <col min="9" max="9" width="11.25" customWidth="1"/>
+    <col min="10" max="10" width="10.25" customWidth="1"/>
+    <col min="11" max="11" width="8.375" customWidth="1"/>
+    <col min="12" max="12" width="25.875" customWidth="1"/>
+    <col min="13" max="13" width="5.75" customWidth="1"/>
+    <col min="14" max="14" width="2.5" customWidth="1"/>
+    <col min="15" max="15" width="8.125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B1" s="17" t="s">
+    <row r="1" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B1" s="17"/>
+      <c r="C1" s="24"/>
+      <c r="D1" s="25" t="s">
         <v>10</v>
       </c>
-      <c r="E1" s="10"/>
-      <c r="F1" s="9"/>
-    </row>
-    <row r="2" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B2" s="18" t="s">
+      <c r="E1" s="25"/>
+      <c r="F1" s="26"/>
+      <c r="G1" s="11"/>
+      <c r="H1" s="11"/>
+      <c r="I1" s="11"/>
+      <c r="J1" s="11"/>
+      <c r="K1" s="11"/>
+    </row>
+    <row r="2" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B2" s="17"/>
+      <c r="C2" s="12"/>
+      <c r="D2" s="27" t="s">
         <v>11</v>
       </c>
-      <c r="E2" s="10"/>
-      <c r="F2" s="9"/>
-      <c r="J2" s="2"/>
-    </row>
-    <row r="3" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B3" s="19" t="s">
+      <c r="E2" s="27"/>
+      <c r="F2" s="28"/>
+      <c r="G2" s="11"/>
+      <c r="H2" s="11"/>
+      <c r="I2" s="11"/>
+      <c r="J2" s="11"/>
+      <c r="K2" s="11"/>
+      <c r="M2" s="2"/>
+    </row>
+    <row r="3" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B3" s="17"/>
+      <c r="C3" s="12"/>
+      <c r="D3" s="27" t="s">
         <v>8</v>
       </c>
-      <c r="E3" s="10"/>
-      <c r="F3" s="9"/>
-    </row>
-    <row r="4" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B4" s="20" t="s">
+      <c r="E3" s="27"/>
+      <c r="F3" s="28"/>
+      <c r="G3" s="11"/>
+      <c r="H3" s="11"/>
+      <c r="I3" s="11"/>
+      <c r="J3" s="11"/>
+      <c r="K3" s="11"/>
+    </row>
+    <row r="4" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B4" s="17"/>
+      <c r="C4" s="12"/>
+      <c r="D4" s="27" t="s">
         <v>12</v>
       </c>
-      <c r="E4" s="10"/>
-      <c r="F4" s="9"/>
-      <c r="G4" s="8"/>
-    </row>
-    <row r="5" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B5" s="21" t="s">
+      <c r="E4" s="27"/>
+      <c r="F4" s="28"/>
+      <c r="G4" s="11"/>
+      <c r="H4" s="11"/>
+      <c r="I4" s="11"/>
+      <c r="J4" s="11"/>
+      <c r="K4" s="11"/>
+    </row>
+    <row r="5" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B5" s="17"/>
+      <c r="C5" s="12"/>
+      <c r="D5" s="27" t="s">
         <v>9</v>
       </c>
-      <c r="E5" s="11"/>
-      <c r="G5" s="9"/>
-      <c r="H5" s="2"/>
-    </row>
-    <row r="6" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="D6" s="4"/>
-      <c r="E6" s="5"/>
-      <c r="F6" s="4"/>
-      <c r="H6" s="2"/>
-      <c r="K6" s="3"/>
-    </row>
-    <row r="7" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="C7" t="s">
+      <c r="E5" s="27"/>
+      <c r="F5" s="28"/>
+      <c r="G5" s="11"/>
+      <c r="H5" s="11"/>
+      <c r="I5" s="11"/>
+      <c r="J5" s="11"/>
+      <c r="K5" s="11"/>
+    </row>
+    <row r="6" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B6" s="18"/>
+      <c r="C6" s="2"/>
+      <c r="D6" s="2"/>
+      <c r="E6" s="2"/>
+      <c r="F6" s="15"/>
+      <c r="G6" s="4"/>
+      <c r="H6" s="5"/>
+      <c r="I6" s="4"/>
+      <c r="K6" s="2"/>
+      <c r="N6" s="3"/>
+    </row>
+    <row r="7" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B7" s="18"/>
+      <c r="C7" s="2"/>
+      <c r="D7" s="27" t="s">
         <v>3</v>
       </c>
-      <c r="D7" s="14" t="s">
+      <c r="E7" s="14"/>
+      <c r="F7" s="16" t="s">
         <v>1</v>
       </c>
-      <c r="E7" s="5"/>
-      <c r="F7" s="4"/>
-      <c r="H7" s="2"/>
-      <c r="I7" s="2"/>
-      <c r="J7" s="2"/>
+      <c r="G7" s="10"/>
+      <c r="H7" s="5"/>
+      <c r="I7" s="4"/>
       <c r="K7" s="2"/>
       <c r="L7" s="2"/>
-    </row>
-    <row r="8" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="D8" s="15" t="s">
+      <c r="M7" s="2"/>
+      <c r="N7" s="2"/>
+      <c r="O7" s="2"/>
+    </row>
+    <row r="8" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B8" s="18"/>
+      <c r="D8" s="27"/>
+      <c r="E8" s="14"/>
+      <c r="F8" s="17" t="s">
         <v>0</v>
       </c>
-      <c r="E8" s="6"/>
-      <c r="F8" s="7"/>
-      <c r="G8" s="1"/>
-      <c r="H8" s="1"/>
-      <c r="I8" s="1"/>
-      <c r="J8" s="2"/>
-      <c r="K8" s="2"/>
-      <c r="L8" s="2"/>
-    </row>
-    <row r="9" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="D9" s="16" t="s">
+      <c r="G8" s="11"/>
+      <c r="H8" s="6"/>
+      <c r="I8" s="7"/>
+      <c r="J8" s="1"/>
+      <c r="K8" s="1"/>
+      <c r="L8" s="1"/>
+      <c r="M8" s="2"/>
+      <c r="N8" s="2"/>
+      <c r="O8" s="2"/>
+    </row>
+    <row r="9" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B9" s="18"/>
+      <c r="D9" s="27"/>
+      <c r="E9" s="14"/>
+      <c r="F9" s="17" t="s">
         <v>2</v>
       </c>
-      <c r="E9" s="2"/>
-      <c r="F9" s="2"/>
-      <c r="G9" s="2"/>
-      <c r="H9" s="1"/>
-      <c r="I9" s="1"/>
-      <c r="J9" s="1"/>
-    </row>
-    <row r="10" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="E10" s="2"/>
-      <c r="F10" s="2"/>
-      <c r="G10" s="2"/>
-    </row>
-    <row r="11" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="C11" s="2" t="s">
+      <c r="G9" s="12"/>
+      <c r="H9" s="2"/>
+      <c r="I9" s="2"/>
+      <c r="J9" s="2"/>
+      <c r="K9" s="1"/>
+      <c r="L9" s="1"/>
+      <c r="M9" s="1"/>
+    </row>
+    <row r="10" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B10" s="18"/>
+      <c r="D10" s="27"/>
+      <c r="E10" s="14"/>
+      <c r="F10" s="18"/>
+      <c r="H10" s="2"/>
+      <c r="I10" s="2"/>
+      <c r="J10" s="2"/>
+    </row>
+    <row r="11" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B11" s="18"/>
+      <c r="C11" s="2"/>
+      <c r="D11" s="22" t="s">
         <v>6</v>
       </c>
-      <c r="D11" s="12" t="s">
+      <c r="E11" s="2"/>
+      <c r="F11" s="19" t="s">
         <v>7</v>
       </c>
-      <c r="F11" s="2"/>
-      <c r="G11" s="2"/>
-    </row>
-    <row r="12" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="G11" s="9"/>
+      <c r="I11" s="2"/>
+      <c r="J11" s="2"/>
+    </row>
+    <row r="12" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B12" s="18"/>
       <c r="C12" s="2"/>
-      <c r="F12" s="2"/>
-      <c r="G12" s="2"/>
-    </row>
-    <row r="13" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="D12" s="2"/>
+      <c r="E12" s="2"/>
+      <c r="F12" s="18"/>
+      <c r="I12" s="2"/>
+      <c r="J12" s="2"/>
+    </row>
+    <row r="13" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B13" s="18"/>
       <c r="C13" s="2"/>
-      <c r="D13" s="13" t="s">
+      <c r="D13" s="27" t="s">
         <v>4</v>
       </c>
-      <c r="F13" s="2"/>
-      <c r="G13" s="2"/>
-    </row>
-    <row r="14" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="D14" s="13" t="s">
+      <c r="E13" s="27"/>
+      <c r="F13" s="28"/>
+      <c r="G13" s="13"/>
+      <c r="I13" s="2"/>
+      <c r="J13" s="2"/>
+    </row>
+    <row r="14" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B14" s="18"/>
+      <c r="C14" s="2"/>
+      <c r="D14" s="27" t="s">
         <v>5</v>
       </c>
-      <c r="E14" s="2"/>
-      <c r="F14" s="2"/>
-      <c r="G14" s="2"/>
-    </row>
-    <row r="15" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="D15" s="2"/>
-      <c r="E15" s="2"/>
-      <c r="F15" s="2"/>
+      <c r="E14" s="27"/>
+      <c r="F14" s="28"/>
+      <c r="G14" s="13"/>
+      <c r="H14" s="2"/>
+      <c r="I14" s="2"/>
+      <c r="J14" s="2"/>
+    </row>
+    <row r="15" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B15" s="18"/>
+      <c r="C15" s="2"/>
+      <c r="D15" s="21"/>
+      <c r="E15" s="21"/>
+      <c r="F15" s="20"/>
       <c r="G15" s="2"/>
-    </row>
-    <row r="16" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="F16" s="9"/>
-      <c r="G16" s="2"/>
-    </row>
-    <row r="17" spans="4:7" x14ac:dyDescent="0.25">
-      <c r="F17" s="9"/>
-      <c r="G17" s="2"/>
-    </row>
-    <row r="18" spans="4:7" x14ac:dyDescent="0.25">
-      <c r="F18" s="9"/>
-      <c r="G18" s="2"/>
-    </row>
-    <row r="19" spans="4:7" x14ac:dyDescent="0.25">
-      <c r="F19" s="9"/>
-      <c r="G19" s="2"/>
-    </row>
-    <row r="20" spans="4:7" x14ac:dyDescent="0.25">
-      <c r="G20" s="2"/>
-    </row>
-    <row r="21" spans="4:7" x14ac:dyDescent="0.25">
-      <c r="D21" s="2"/>
-      <c r="E21" s="2"/>
+      <c r="H15" s="2"/>
+      <c r="I15" s="2"/>
+      <c r="J15" s="2"/>
+    </row>
+    <row r="16" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="C16" s="23"/>
+      <c r="I16" s="8"/>
+      <c r="J16" s="2"/>
+    </row>
+    <row r="17" spans="6:10" x14ac:dyDescent="0.25">
+      <c r="I17" s="8"/>
+      <c r="J17" s="2"/>
+    </row>
+    <row r="18" spans="6:10" x14ac:dyDescent="0.25">
+      <c r="I18" s="8"/>
+      <c r="J18" s="2"/>
+    </row>
+    <row r="19" spans="6:10" x14ac:dyDescent="0.25">
+      <c r="I19" s="8"/>
+      <c r="J19" s="2"/>
+    </row>
+    <row r="20" spans="6:10" x14ac:dyDescent="0.25">
+      <c r="J20" s="2"/>
+    </row>
+    <row r="21" spans="6:10" x14ac:dyDescent="0.25">
       <c r="F21" s="2"/>
       <c r="G21" s="2"/>
-    </row>
-    <row r="22" spans="4:7" x14ac:dyDescent="0.25">
-      <c r="D22" s="2"/>
-      <c r="E22" s="2"/>
+      <c r="H21" s="2"/>
+      <c r="I21" s="2"/>
+      <c r="J21" s="2"/>
+    </row>
+    <row r="22" spans="6:10" x14ac:dyDescent="0.25">
       <c r="F22" s="2"/>
       <c r="G22" s="2"/>
-    </row>
-    <row r="23" spans="4:7" x14ac:dyDescent="0.25">
-      <c r="D23" s="2"/>
-      <c r="E23" s="2"/>
+      <c r="H22" s="2"/>
+      <c r="I22" s="2"/>
+      <c r="J22" s="2"/>
+    </row>
+    <row r="23" spans="6:10" x14ac:dyDescent="0.25">
       <c r="F23" s="2"/>
       <c r="G23" s="2"/>
-    </row>
-    <row r="24" spans="4:7" x14ac:dyDescent="0.25">
-      <c r="D24" s="2"/>
-      <c r="E24" s="2"/>
+      <c r="H23" s="2"/>
+      <c r="I23" s="2"/>
+      <c r="J23" s="2"/>
+    </row>
+    <row r="24" spans="6:10" x14ac:dyDescent="0.25">
       <c r="F24" s="2"/>
       <c r="G24" s="2"/>
-    </row>
-    <row r="25" spans="4:7" x14ac:dyDescent="0.25">
-      <c r="D25" s="2"/>
-      <c r="E25" s="2"/>
+      <c r="H24" s="2"/>
+      <c r="I24" s="2"/>
+      <c r="J24" s="2"/>
+    </row>
+    <row r="25" spans="6:10" x14ac:dyDescent="0.25">
       <c r="F25" s="2"/>
       <c r="G25" s="2"/>
-    </row>
-    <row r="26" spans="4:7" x14ac:dyDescent="0.25">
-      <c r="D26" s="2"/>
-      <c r="E26" s="2"/>
+      <c r="H25" s="2"/>
+      <c r="I25" s="2"/>
+      <c r="J25" s="2"/>
+    </row>
+    <row r="26" spans="6:10" x14ac:dyDescent="0.25">
       <c r="F26" s="2"/>
       <c r="G26" s="2"/>
-    </row>
-    <row r="27" spans="4:7" x14ac:dyDescent="0.25">
-      <c r="D27" s="2"/>
-      <c r="E27" s="2"/>
+      <c r="H26" s="2"/>
+      <c r="I26" s="2"/>
+      <c r="J26" s="2"/>
+    </row>
+    <row r="27" spans="6:10" x14ac:dyDescent="0.25">
       <c r="F27" s="2"/>
       <c r="G27" s="2"/>
-    </row>
-    <row r="28" spans="4:7" x14ac:dyDescent="0.25">
-      <c r="D28" s="2"/>
-      <c r="E28" s="2"/>
+      <c r="H27" s="2"/>
+      <c r="I27" s="2"/>
+      <c r="J27" s="2"/>
+    </row>
+    <row r="28" spans="6:10" x14ac:dyDescent="0.25">
       <c r="F28" s="2"/>
       <c r="G28" s="2"/>
-    </row>
-    <row r="29" spans="4:7" x14ac:dyDescent="0.25">
-      <c r="G29" s="2"/>
-    </row>
-    <row r="47" spans="8:8" x14ac:dyDescent="0.25">
-      <c r="H47" s="2"/>
-    </row>
-    <row r="48" spans="8:8" x14ac:dyDescent="0.25">
-      <c r="H48" s="2"/>
-    </row>
-    <row r="49" spans="8:12" x14ac:dyDescent="0.25">
-      <c r="H49" s="2"/>
-      <c r="I49" s="2"/>
-      <c r="J49" s="2"/>
+      <c r="H28" s="2"/>
+      <c r="I28" s="2"/>
+      <c r="J28" s="2"/>
+    </row>
+    <row r="29" spans="6:10" x14ac:dyDescent="0.25">
+      <c r="J29" s="2"/>
+    </row>
+    <row r="47" spans="11:11" x14ac:dyDescent="0.25">
+      <c r="K47" s="2"/>
+    </row>
+    <row r="48" spans="11:11" x14ac:dyDescent="0.25">
+      <c r="K48" s="2"/>
+    </row>
+    <row r="49" spans="11:15" x14ac:dyDescent="0.25">
       <c r="K49" s="2"/>
-    </row>
-    <row r="50" spans="8:12" x14ac:dyDescent="0.25">
-      <c r="H50" s="2"/>
-      <c r="I50" s="2"/>
-      <c r="J50" s="2"/>
+      <c r="L49" s="2"/>
+      <c r="M49" s="2"/>
+      <c r="N49" s="2"/>
+    </row>
+    <row r="50" spans="11:15" x14ac:dyDescent="0.25">
       <c r="K50" s="2"/>
       <c r="L50" s="2"/>
-    </row>
-    <row r="51" spans="8:12" x14ac:dyDescent="0.25">
-      <c r="H51" s="2"/>
-      <c r="I51" s="2"/>
-      <c r="J51" s="2"/>
+      <c r="M50" s="2"/>
+      <c r="N50" s="2"/>
+      <c r="O50" s="2"/>
+    </row>
+    <row r="51" spans="11:15" x14ac:dyDescent="0.25">
       <c r="K51" s="2"/>
       <c r="L51" s="2"/>
-    </row>
-    <row r="52" spans="8:12" x14ac:dyDescent="0.25">
-      <c r="H52" s="2"/>
-      <c r="I52" s="2"/>
-      <c r="J52" s="2"/>
+      <c r="M51" s="2"/>
+      <c r="N51" s="2"/>
+      <c r="O51" s="2"/>
+    </row>
+    <row r="52" spans="11:15" x14ac:dyDescent="0.25">
       <c r="K52" s="2"/>
       <c r="L52" s="2"/>
-    </row>
-    <row r="53" spans="8:12" x14ac:dyDescent="0.25">
-      <c r="H53" s="2"/>
-      <c r="I53" s="2"/>
-      <c r="J53" s="2"/>
+      <c r="M52" s="2"/>
+      <c r="N52" s="2"/>
+      <c r="O52" s="2"/>
+    </row>
+    <row r="53" spans="11:15" x14ac:dyDescent="0.25">
       <c r="K53" s="2"/>
       <c r="L53" s="2"/>
-    </row>
-    <row r="54" spans="8:12" x14ac:dyDescent="0.25">
-      <c r="H54" s="2"/>
-      <c r="I54" s="2"/>
-      <c r="J54" s="2"/>
+      <c r="M53" s="2"/>
+      <c r="N53" s="2"/>
+      <c r="O53" s="2"/>
+    </row>
+    <row r="54" spans="11:15" x14ac:dyDescent="0.25">
       <c r="K54" s="2"/>
       <c r="L54" s="2"/>
-    </row>
-    <row r="55" spans="8:12" x14ac:dyDescent="0.25">
-      <c r="H55" s="2"/>
-      <c r="I55" s="2"/>
-      <c r="J55" s="2"/>
+      <c r="M54" s="2"/>
+      <c r="N54" s="2"/>
+      <c r="O54" s="2"/>
+    </row>
+    <row r="55" spans="11:15" x14ac:dyDescent="0.25">
       <c r="K55" s="2"/>
       <c r="L55" s="2"/>
-    </row>
-    <row r="56" spans="8:12" x14ac:dyDescent="0.25">
-      <c r="H56" s="2"/>
-      <c r="I56" s="2"/>
-      <c r="J56" s="2"/>
+      <c r="M55" s="2"/>
+      <c r="N55" s="2"/>
+      <c r="O55" s="2"/>
+    </row>
+    <row r="56" spans="11:15" x14ac:dyDescent="0.25">
       <c r="K56" s="2"/>
       <c r="L56" s="2"/>
-    </row>
-    <row r="57" spans="8:12" x14ac:dyDescent="0.25">
-      <c r="H57" s="2"/>
-      <c r="I57" s="2"/>
-      <c r="J57" s="2"/>
+      <c r="M56" s="2"/>
+      <c r="N56" s="2"/>
+      <c r="O56" s="2"/>
+    </row>
+    <row r="57" spans="11:15" x14ac:dyDescent="0.25">
       <c r="K57" s="2"/>
       <c r="L57" s="2"/>
-    </row>
-    <row r="58" spans="8:12" x14ac:dyDescent="0.25">
-      <c r="H58" s="2"/>
-      <c r="I58" s="2"/>
-      <c r="J58" s="2"/>
+      <c r="M57" s="2"/>
+      <c r="N57" s="2"/>
+      <c r="O57" s="2"/>
+    </row>
+    <row r="58" spans="11:15" x14ac:dyDescent="0.25">
       <c r="K58" s="2"/>
       <c r="L58" s="2"/>
-    </row>
-    <row r="59" spans="8:12" x14ac:dyDescent="0.25">
-      <c r="H59" s="2"/>
-      <c r="I59" s="2"/>
-      <c r="J59" s="2"/>
+      <c r="M58" s="2"/>
+      <c r="N58" s="2"/>
+      <c r="O58" s="2"/>
+    </row>
+    <row r="59" spans="11:15" x14ac:dyDescent="0.25">
       <c r="K59" s="2"/>
       <c r="L59" s="2"/>
-    </row>
-    <row r="60" spans="8:12" x14ac:dyDescent="0.25">
-      <c r="H60" s="2"/>
-      <c r="I60" s="2"/>
-      <c r="J60" s="2"/>
+      <c r="M59" s="2"/>
+      <c r="N59" s="2"/>
+      <c r="O59" s="2"/>
+    </row>
+    <row r="60" spans="11:15" x14ac:dyDescent="0.25">
       <c r="K60" s="2"/>
       <c r="L60" s="2"/>
-    </row>
-    <row r="61" spans="8:12" x14ac:dyDescent="0.25">
-      <c r="H61" s="2"/>
-      <c r="I61" s="2"/>
-      <c r="J61" s="2"/>
+      <c r="M60" s="2"/>
+      <c r="N60" s="2"/>
+      <c r="O60" s="2"/>
+    </row>
+    <row r="61" spans="11:15" x14ac:dyDescent="0.25">
       <c r="K61" s="2"/>
       <c r="L61" s="2"/>
-    </row>
-    <row r="62" spans="8:12" x14ac:dyDescent="0.25">
-      <c r="H62" s="2"/>
-      <c r="I62" s="2"/>
-      <c r="J62" s="2"/>
+      <c r="M61" s="2"/>
+      <c r="N61" s="2"/>
+      <c r="O61" s="2"/>
+    </row>
+    <row r="62" spans="11:15" x14ac:dyDescent="0.25">
       <c r="K62" s="2"/>
       <c r="L62" s="2"/>
-    </row>
-    <row r="63" spans="8:12" x14ac:dyDescent="0.25">
-      <c r="H63" s="2"/>
-      <c r="I63" s="2"/>
-      <c r="J63" s="2"/>
+      <c r="M62" s="2"/>
+      <c r="N62" s="2"/>
+      <c r="O62" s="2"/>
+    </row>
+    <row r="63" spans="11:15" x14ac:dyDescent="0.25">
       <c r="K63" s="2"/>
       <c r="L63" s="2"/>
-    </row>
-    <row r="64" spans="8:12" x14ac:dyDescent="0.25">
-      <c r="H64" s="2"/>
-      <c r="I64" s="2"/>
-      <c r="J64" s="2"/>
+      <c r="M63" s="2"/>
+      <c r="N63" s="2"/>
+      <c r="O63" s="2"/>
+    </row>
+    <row r="64" spans="11:15" x14ac:dyDescent="0.25">
       <c r="K64" s="2"/>
       <c r="L64" s="2"/>
-    </row>
-    <row r="65" spans="9:13" x14ac:dyDescent="0.25">
-      <c r="I65" s="2"/>
-      <c r="J65" s="2"/>
-      <c r="K65" s="2"/>
+      <c r="M64" s="2"/>
+      <c r="N64" s="2"/>
+      <c r="O64" s="2"/>
+    </row>
+    <row r="65" spans="12:16" x14ac:dyDescent="0.25">
       <c r="L65" s="2"/>
-    </row>
-    <row r="66" spans="9:13" x14ac:dyDescent="0.25">
-      <c r="I66" s="2"/>
-      <c r="J66" s="2"/>
-      <c r="K66" s="2"/>
+      <c r="M65" s="2"/>
+      <c r="N65" s="2"/>
+      <c r="O65" s="2"/>
+    </row>
+    <row r="66" spans="12:16" x14ac:dyDescent="0.25">
       <c r="L66" s="2"/>
       <c r="M66" s="2"/>
+      <c r="N66" s="2"/>
+      <c r="O66" s="2"/>
+      <c r="P66" s="2"/>
     </row>
   </sheetData>
+  <mergeCells count="8">
+    <mergeCell ref="D14:F14"/>
+    <mergeCell ref="D13:F13"/>
+    <mergeCell ref="D7:D10"/>
+    <mergeCell ref="D1:F1"/>
+    <mergeCell ref="D2:F2"/>
+    <mergeCell ref="D3:F3"/>
+    <mergeCell ref="D4:F4"/>
+    <mergeCell ref="D5:F5"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="172" orientation="landscape" horizontalDpi="200" verticalDpi="200" r:id="rId1"/>
 </worksheet>
